--- a/addons/account/static/xls/aml_import_template.xlsx
+++ b/addons/account/static/xls/aml_import_template.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">MISC/2021/00002</t>
   </si>
   <si>
-    <t xml:space="preserve">Deco Addict</t>
+    <t xml:space="preserve">Acme Corporation</t>
   </si>
   <si>
     <t xml:space="preserve">[FURN_8220] Four Person Desk</t>
